--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>spu</t>
   </si>
@@ -61,163 +61,25 @@
     <t>销售方式</t>
   </si>
   <si>
-    <t>品名</t>
-  </si>
-  <si>
-    <t>品名（英文）</t>
-  </si>
-  <si>
-    <t>产品类型</t>
-  </si>
-  <si>
-    <t>迭代产品</t>
-  </si>
-  <si>
     <t>产品属性</t>
   </si>
   <si>
-    <t>品牌</t>
-  </si>
-  <si>
     <t>产品开发状态</t>
   </si>
   <si>
-    <t>产品等级</t>
-  </si>
-  <si>
-    <t>销售渠道</t>
-  </si>
-  <si>
-    <t>是否客户定制</t>
-  </si>
-  <si>
-    <t>模具成本(￥)</t>
-  </si>
-  <si>
-    <t>委托开发成本(￥)</t>
-  </si>
-  <si>
-    <t>产品卖点</t>
-  </si>
-  <si>
-    <t>产品功能描述</t>
-  </si>
-  <si>
-    <t>产品用途</t>
-  </si>
-  <si>
-    <t>计划上市时间</t>
-  </si>
-  <si>
-    <t>存在侵权风险(是/否)</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>主要材质</t>
-  </si>
-  <si>
-    <t>预计立项成本(￥)</t>
-  </si>
-  <si>
-    <t>实际量产成本(￥)</t>
-  </si>
-  <si>
-    <t>预计项目成本(￥)</t>
-  </si>
-  <si>
-    <t>税率</t>
-  </si>
-  <si>
-    <t>目标含税成本(￥)</t>
-  </si>
-  <si>
-    <t>目标不含税成本(￥)</t>
-  </si>
-  <si>
-    <t>标准零售价(￥)</t>
-  </si>
-  <si>
-    <t>ean码</t>
-  </si>
-  <si>
-    <t>MOQ(最小起订量)</t>
-  </si>
-  <si>
-    <t>试产数量</t>
-  </si>
-  <si>
-    <t>首批量产数量</t>
-  </si>
-  <si>
-    <t>计划首批下单量</t>
-  </si>
-  <si>
-    <t>实际首批到货量</t>
-  </si>
-  <si>
-    <t>预计首批到货时间</t>
-  </si>
-  <si>
-    <t>实际首批到货时间</t>
-  </si>
-  <si>
-    <t>首批下单时间</t>
-  </si>
-  <si>
-    <t>交货周期(天)</t>
-  </si>
-  <si>
     <t>采购员</t>
   </si>
   <si>
-    <t>首批到货状态</t>
-  </si>
-  <si>
     <t>一级供应商</t>
   </si>
   <si>
     <t>二级供应商</t>
   </si>
   <si>
-    <t>年目标销量</t>
-  </si>
-  <si>
-    <t>年目标销售额（￥）</t>
-  </si>
-  <si>
-    <t>目标月销售量</t>
-  </si>
-  <si>
-    <t>目标月销售额（￥）</t>
-  </si>
-  <si>
-    <t>首季度目标销量</t>
-  </si>
-  <si>
-    <t>销售国家</t>
-  </si>
-  <si>
-    <t>图片是否完成</t>
-  </si>
-  <si>
-    <t>视频是否完成</t>
-  </si>
-  <si>
-    <t>退市时间</t>
-  </si>
-  <si>
     <t>销售状态</t>
   </si>
   <si>
-    <t>产品上市(含培训)资料链接</t>
-  </si>
-  <si>
     <t>是否可销售</t>
-  </si>
-  <si>
-    <t>销售平台</t>
   </si>
   <si>
     <t xml:space="preserve">报关产品属性
@@ -979,7 +841,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1007,37 +869,28 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1429,7 +1282,7 @@
     <col min="81" max="82" width="11.125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:82">
+    <row r="1" s="1" customFormat="1" spans="1:36">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1475,235 +1328,109 @@
       <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="11" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="S1" s="9" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="U1" s="12" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="W1" s="9" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Y1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="Z1" s="13" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AB1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AC1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AD1" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AE1" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AF1" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="11" t="s">
+      <c r="AG1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="9" t="s">
+      <c r="AH1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="14" t="s">
+      <c r="AI1" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="14" t="s">
+      <c r="AJ1" s="15" t="s">
         <v>35</v>
-      </c>
-      <c r="AK1" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="BE1" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="BF1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="BI1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="BJ1" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="BK1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="BM1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="BN1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="BO1" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="BP1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="BQ1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="BR1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BS1" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="BT1" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="BU1" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="BV1" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="BW1" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="BX1" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="BY1" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="BZ1" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="CA1" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="CB1" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="CC1" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="CD1" s="19" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="80:82">
-      <c r="CB2" s="18"/>
-      <c r="CC2" s="18"/>
-      <c r="CD2" s="18"/>
+      <c r="CB2" s="16"/>
+      <c r="CC2" s="16"/>
+      <c r="CD2" s="16"/>
     </row>
   </sheetData>
   <dataValidations count="19">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
-      <formula1>"新产品,迭代产品"</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BJ$1:BJ$1048576 BU$1:BV$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P1 AA1:AB1 R2:R1048576 AG2:AG1048576 AY2:AY1048576 BJ2:BJ1048576 BU2:BV1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1:Z1 AC1 AF1:AG1 AF2:AF1048576 BW2:BW1048576 BS2:BT1048576 BZ2:CA1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD1 AW2:AW1048576 BX2:BX1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE1 U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BY2:BY1048576 BA3:BB1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH1 AZ2:AZ1048576 CB2:CB1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+      <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 Z2:Z1048576 AC2:AD1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BY$1:BY$1048576 BA3:BB1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576 BC3:BC1048576">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:W$1048576 AP$1:AP$1048576 BD2:BD1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576 AP2:AP1048576 BD2:BD1048576">
       <formula1>1</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
@@ -1711,30 +1438,18 @@
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BW$1:BW$1048576 BS$1:BT$1048576 BZ$1:CA$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AI1048576 AM2:AM1048576 AV2:AV1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576 AV2:AV1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ$1:AQ$1048576 AJ$1:AL$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ2:AQ1048576 AJ2:AL1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BX$1:BX$1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999999</formula2>
     </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576">
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CB$1:CB$1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF3:BF1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
@@ -1754,7 +1469,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN$1:AO$1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN2:AO1048576">
       <formula1>32874</formula1>
       <formula2>2958464</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>spu</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>二级供应商</t>
+  </si>
+  <si>
+    <t>年目标销量</t>
   </si>
   <si>
     <t>销售状态</t>
@@ -171,16 +174,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0000_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="179" formatCode="0_ "/>
-    <numFmt numFmtId="180" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -841,7 +842,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -854,43 +855,34 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1212,273 +1204,197 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CD2"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
-    <col min="10" max="10" width="10.5" customWidth="1"/>
-    <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="7.75" customWidth="1"/>
-    <col min="14" max="14" width="12.75" customWidth="1"/>
-    <col min="17" max="17" width="11.5" customWidth="1"/>
-    <col min="18" max="18" width="12.125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="14.375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="15.375" customWidth="1"/>
-    <col min="21" max="21" width="15.875" customWidth="1"/>
-    <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="12" style="3" customWidth="1"/>
-    <col min="24" max="24" width="16.625" customWidth="1"/>
-    <col min="25" max="25" width="5.875" customWidth="1"/>
-    <col min="26" max="26" width="9.75" customWidth="1"/>
-    <col min="27" max="27" width="15.125" style="4" customWidth="1"/>
-    <col min="28" max="28" width="15" style="2" customWidth="1"/>
-    <col min="29" max="29" width="14.875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="8.75" style="2" customWidth="1"/>
-    <col min="31" max="31" width="15.25" style="2" customWidth="1"/>
-    <col min="32" max="32" width="16.75" style="2" customWidth="1"/>
-    <col min="33" max="33" width="14" style="2" customWidth="1"/>
-    <col min="34" max="34" width="11.5" style="5"/>
-    <col min="35" max="35" width="13" style="6" customWidth="1"/>
-    <col min="36" max="36" width="12.25" style="6" customWidth="1"/>
-    <col min="37" max="37" width="11.125" style="6" customWidth="1"/>
-    <col min="38" max="38" width="13.625" style="6" customWidth="1"/>
-    <col min="39" max="39" width="12.625" style="6" customWidth="1"/>
-    <col min="40" max="40" width="14.25" style="3" customWidth="1"/>
-    <col min="41" max="41" width="14.5" style="3" customWidth="1"/>
-    <col min="42" max="42" width="12" style="3" customWidth="1"/>
-    <col min="43" max="43" width="10.75" style="6" customWidth="1"/>
-    <col min="45" max="45" width="10.75" customWidth="1"/>
-    <col min="46" max="46" width="16.375" customWidth="1"/>
-    <col min="47" max="47" width="12.375" customWidth="1"/>
-    <col min="48" max="48" width="11.5" style="6" customWidth="1"/>
-    <col min="49" max="49" width="15.875" style="2" customWidth="1"/>
-    <col min="50" max="50" width="11.625" style="6" customWidth="1"/>
-    <col min="51" max="51" width="15.875" style="2" customWidth="1"/>
-    <col min="52" max="52" width="13.5" style="6" customWidth="1"/>
-    <col min="54" max="54" width="11.75" customWidth="1"/>
-    <col min="55" max="55" width="12" customWidth="1"/>
-    <col min="56" max="56" width="11" style="3" customWidth="1"/>
-    <col min="57" max="57" width="9.125" customWidth="1"/>
-    <col min="58" max="58" width="21.5" customWidth="1"/>
-    <col min="59" max="59" width="10.25" customWidth="1"/>
-    <col min="60" max="60" width="9.375" customWidth="1"/>
-    <col min="61" max="61" width="12.75" customWidth="1"/>
-    <col min="62" max="62" width="12.75" style="2" customWidth="1"/>
-    <col min="63" max="63" width="13.75" customWidth="1"/>
-    <col min="64" max="64" width="13.375" customWidth="1"/>
-    <col min="65" max="65" width="11.75" customWidth="1"/>
-    <col min="66" max="66" width="9.875" customWidth="1"/>
-    <col min="67" max="67" width="10" customWidth="1"/>
-    <col min="68" max="68" width="11" customWidth="1"/>
-    <col min="69" max="69" width="9.375"/>
-    <col min="71" max="71" width="11.875" style="7" customWidth="1"/>
-    <col min="72" max="72" width="12.5" style="7" customWidth="1"/>
-    <col min="73" max="73" width="12.125" style="7" customWidth="1"/>
-    <col min="74" max="79" width="9" style="7"/>
-    <col min="80" max="80" width="9" style="6"/>
-    <col min="81" max="82" width="11.125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="12.75" customWidth="1"/>
+    <col min="11" max="11" width="16.375" customWidth="1"/>
+    <col min="12" max="12" width="12.375" customWidth="1"/>
+    <col min="13" max="13" width="11.5" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9.125" customWidth="1"/>
+    <col min="15" max="15" width="10.25" customWidth="1"/>
+    <col min="16" max="16" width="12.75" customWidth="1"/>
+    <col min="17" max="17" width="12.75" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.75" customWidth="1"/>
+    <col min="19" max="19" width="13.375" customWidth="1"/>
+    <col min="20" max="20" width="11.75" customWidth="1"/>
+    <col min="21" max="21" width="9.875" customWidth="1"/>
+    <col min="22" max="22" width="10" customWidth="1"/>
+    <col min="23" max="23" width="11" customWidth="1"/>
+    <col min="24" max="24" width="9.375"/>
+    <col min="26" max="26" width="11.875" style="4" customWidth="1"/>
+    <col min="27" max="27" width="12.5" style="4" customWidth="1"/>
+    <col min="28" max="28" width="12.125" style="4" customWidth="1"/>
+    <col min="29" max="34" width="9" style="4"/>
+    <col min="35" max="35" width="9" style="2"/>
+    <col min="36" max="37" width="11.125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:36">
-      <c r="A1" s="9" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:37">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="V1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="13" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="Z1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="13" t="s">
+      <c r="AA1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="13" t="s">
+      <c r="AB1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="13" t="s">
+      <c r="AC1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="13" t="s">
+      <c r="AD1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="13" t="s">
+      <c r="AE1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="13" t="s">
+      <c r="AF1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="13" t="s">
+      <c r="AG1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="14" t="s">
+      <c r="AH1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="15" t="s">
+      <c r="AI1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="15" t="s">
+      <c r="AJ1" s="12" t="s">
         <v>35</v>
       </c>
+      <c r="AK1" s="12" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="80:82">
-      <c r="CB2" s="16"/>
-      <c r="CC2" s="16"/>
-      <c r="CD2" s="16"/>
+    <row r="2" spans="35:37">
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="13"/>
     </row>
   </sheetData>
-  <dataValidations count="19">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P1 AA1:AB1 R2:R1048576 AG2:AG1048576 AY2:AY1048576 BJ2:BJ1048576 BU2:BV1048576">
+  <dataValidations count="10">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L1048576 AF$1:AF$1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+21</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576 AB$1:AC$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1:Z1 AC1 AF1:AG1 AF2:AF1048576 BW2:BW1048576 BS2:BT1048576 BZ2:CA1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900000</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y1048576">
+      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576 Z$1:AA$1048576 AG$1:AH$1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD1 AW2:AW1048576 BX2:BX1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE$1:AE$1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE1 U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BY2:BY1048576 BA3:BB1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH1 AZ2:AZ1048576 CB2:CB1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
-      <formula1>"新产品,迭代产品"</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 Z2:Z1048576 AC2:AD1048576">
-      <formula1>0</formula1>
-      <formula2>999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576 BC3:BC1048576">
-      <formula1>0</formula1>
-      <formula2>9999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576 AP2:AP1048576 BD2:BD1048576">
-      <formula1>1</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576 AA2:AA1048576 AE2:AE1048576">
-      <formula1>0</formula1>
-      <formula2>99999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AI1048576 AM2:AM1048576 AV2:AV1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ2:AQ1048576 AJ2:AL1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF3:BF1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+23</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+21</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL3:BL1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900000</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ3:BQ1048576">
-      <formula1>25569</formula1>
-      <formula2>72686</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR1048576">
-      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN2:AO1048576">
-      <formula1>32874</formula1>
-      <formula2>2958464</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="AX3:AX1048573" listDataValidation="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -27,12 +27,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>spu</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -76,9 +83,6 @@
     <t>二级供应商</t>
   </si>
   <si>
-    <t>年目标销量</t>
-  </si>
-  <si>
     <t>销售状态</t>
   </si>
   <si>
@@ -90,6 +94,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>报关申报价（</t>
     </r>
     <r>
@@ -179,9 +189,9 @@
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.0000_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.0000_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -870,19 +880,19 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1204,7 +1214,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -1213,27 +1223,26 @@
     <col min="9" max="9" width="12.75" customWidth="1"/>
     <col min="11" max="11" width="16.375" customWidth="1"/>
     <col min="12" max="12" width="12.375" customWidth="1"/>
-    <col min="13" max="13" width="11.5" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.125" customWidth="1"/>
-    <col min="15" max="15" width="10.25" customWidth="1"/>
-    <col min="16" max="16" width="12.75" customWidth="1"/>
-    <col min="17" max="17" width="12.75" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.75" customWidth="1"/>
-    <col min="19" max="19" width="13.375" customWidth="1"/>
-    <col min="20" max="20" width="11.75" customWidth="1"/>
-    <col min="21" max="21" width="9.875" customWidth="1"/>
-    <col min="22" max="22" width="10" customWidth="1"/>
-    <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="9.375"/>
-    <col min="26" max="26" width="11.875" style="4" customWidth="1"/>
-    <col min="27" max="27" width="12.5" style="4" customWidth="1"/>
-    <col min="28" max="28" width="12.125" style="4" customWidth="1"/>
-    <col min="29" max="34" width="9" style="4"/>
-    <col min="35" max="35" width="9" style="2"/>
-    <col min="36" max="37" width="11.125" style="5" customWidth="1"/>
+    <col min="13" max="13" width="9.125" customWidth="1"/>
+    <col min="14" max="14" width="10.25" customWidth="1"/>
+    <col min="15" max="15" width="12.75" customWidth="1"/>
+    <col min="16" max="16" width="12.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="13.75" customWidth="1"/>
+    <col min="18" max="18" width="13.375" customWidth="1"/>
+    <col min="19" max="19" width="11.75" customWidth="1"/>
+    <col min="20" max="20" width="9.875" customWidth="1"/>
+    <col min="21" max="21" width="10" customWidth="1"/>
+    <col min="22" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="9.375"/>
+    <col min="25" max="25" width="11.875" style="3" customWidth="1"/>
+    <col min="26" max="26" width="12.5" style="3" customWidth="1"/>
+    <col min="27" max="27" width="12.125" style="3" customWidth="1"/>
+    <col min="28" max="33" width="9" style="3"/>
+    <col min="34" max="34" width="9" style="4"/>
+    <col min="35" max="36" width="11.125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:37">
+    <row r="1" s="1" customFormat="1" spans="1:36">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1270,7 +1279,7 @@
       <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="6" t="s">
@@ -1279,10 +1288,10 @@
       <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="6" t="s">
@@ -1294,10 +1303,10 @@
       <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="6" t="s">
@@ -1306,89 +1315,82 @@
       <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="Z1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AA1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AB1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AC1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AD1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AE1" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AF1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="11" t="s">
+      <c r="AG1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="AH1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="8" t="s">
+      <c r="AI1" s="12" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="12" t="s">
-        <v>36</v>
-      </c>
     </row>
-    <row r="2" spans="35:37">
+    <row r="2" spans="34:36">
+      <c r="AH2" s="13"/>
       <c r="AI2" s="13"/>
       <c r="AJ2" s="13"/>
-      <c r="AK2" s="13"/>
     </row>
   </sheetData>
-  <dataValidations count="10">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L1048576 AF$1:AF$1048576">
+  <dataValidations count="9">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L1048576 AE$1:AE$1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+21</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P$1:P$1048576 AA$1:AB$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900000</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3:W1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X1048576">
+      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC$1:AC$1048576 Y$1:Z$1048576 AF$1:AG$1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+21</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576 AB$1:AC$1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900000</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X1048576">
-      <formula1>25569</formula1>
-      <formula2>72686</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y1048576">
-      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576 Z$1:AA$1048576 AG$1:AH$1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE$1:AE$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH$1:AH$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -1358,14 +1358,10 @@
       <c r="AJ2" s="13"/>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="8">
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L1048576 AE$1:AE$1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P$1:P$1048576 AA$1:AB$1048576">
       <formula1>0</formula1>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>spu</t>
   </si>
@@ -91,6 +91,9 @@
   <si>
     <t xml:space="preserve">报关产品属性
 </t>
+  </si>
+  <si>
+    <t>保险属性</t>
   </si>
   <si>
     <r>
@@ -1214,7 +1217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -1226,23 +1229,23 @@
     <col min="13" max="13" width="9.125" customWidth="1"/>
     <col min="14" max="14" width="10.25" customWidth="1"/>
     <col min="15" max="15" width="12.75" customWidth="1"/>
-    <col min="16" max="16" width="12.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="13.75" customWidth="1"/>
-    <col min="18" max="18" width="13.375" customWidth="1"/>
-    <col min="19" max="19" width="11.75" customWidth="1"/>
-    <col min="20" max="20" width="9.875" customWidth="1"/>
-    <col min="21" max="21" width="10" customWidth="1"/>
-    <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="9.375"/>
-    <col min="25" max="25" width="11.875" style="3" customWidth="1"/>
-    <col min="26" max="26" width="12.5" style="3" customWidth="1"/>
-    <col min="27" max="27" width="12.125" style="3" customWidth="1"/>
-    <col min="28" max="33" width="9" style="3"/>
-    <col min="34" max="34" width="9" style="4"/>
-    <col min="35" max="36" width="11.125" style="5" customWidth="1"/>
+    <col min="16" max="17" width="12.75" style="2" customWidth="1"/>
+    <col min="18" max="18" width="13.75" customWidth="1"/>
+    <col min="19" max="19" width="13.375" customWidth="1"/>
+    <col min="20" max="20" width="11.75" customWidth="1"/>
+    <col min="21" max="21" width="9.875" customWidth="1"/>
+    <col min="22" max="22" width="10" customWidth="1"/>
+    <col min="23" max="23" width="11" customWidth="1"/>
+    <col min="24" max="24" width="9.375"/>
+    <col min="26" max="26" width="11.875" style="3" customWidth="1"/>
+    <col min="27" max="27" width="12.5" style="3" customWidth="1"/>
+    <col min="28" max="28" width="12.125" style="3" customWidth="1"/>
+    <col min="29" max="34" width="9" style="3"/>
+    <col min="35" max="35" width="9" style="4"/>
+    <col min="36" max="37" width="11.125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:36">
+    <row r="1" s="1" customFormat="1" spans="1:37">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1291,7 +1294,7 @@
       <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="6" t="s">
@@ -1303,10 +1306,10 @@
       <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="9" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="6" t="s">
@@ -1315,7 +1318,7 @@
       <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="10" t="s">
@@ -1342,51 +1345,54 @@
       <c r="AG1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="11" t="s">
+      <c r="AH1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="12" t="s">
+      <c r="AI1" s="11" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="12" t="s">
         <v>35</v>
       </c>
+      <c r="AK1" s="12" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="34:36">
-      <c r="AH2" s="13"/>
+    <row r="2" spans="35:37">
       <c r="AI2" s="13"/>
       <c r="AJ2" s="13"/>
+      <c r="AK2" s="13"/>
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L1048576 AE$1:AE$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L1048576 AF$1:AF$1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P$1:P$1048576 AA$1:AB$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576 AB$1:AC$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3:W1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC$1:AC$1048576 Y$1:Z$1048576 AF$1:AG$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576 Z$1:AA$1048576 AG$1:AH$1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE$1:AE$1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH$1:AH$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
@@ -147,22 +147,22 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)</t>
-  </si>
-  <si>
-    <t>箱规(长)</t>
-  </si>
-  <si>
-    <t>箱规(宽)</t>
-  </si>
-  <si>
-    <t>箱规(高)</t>
+    <t>产品尺寸(长)(cm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)(cm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)(cm)</t>
+  </si>
+  <si>
+    <t>箱规(长)(cm)</t>
+  </si>
+  <si>
+    <t>箱规(宽)(cm)</t>
+  </si>
+  <si>
+    <t>箱规(高)(cm)</t>
   </si>
   <si>
     <t>毛重</t>
@@ -1369,7 +1369,7 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576 AB$1:AC$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576 AB2:AC1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -1384,11 +1384,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576 Z$1:AA$1048576 AG$1:AH$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576 AG$1:AH$1048576 Z2:AA1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE$1:AE$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
@@ -147,22 +147,22 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(长)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(宽)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(高)(cm)</t>
+    <t>产品尺寸(长)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)</t>
+  </si>
+  <si>
+    <t>箱规(长)</t>
+  </si>
+  <si>
+    <t>箱规(宽)</t>
+  </si>
+  <si>
+    <t>箱规(高)</t>
   </si>
   <si>
     <t>毛重</t>
@@ -1369,7 +1369,7 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576 AB2:AC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576 AB$1:AC$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -1384,11 +1384,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576 AG$1:AH$1048576 Z2:AA1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576 Z$1:AA$1048576 AG$1:AH$1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE$1:AE$1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -165,13 +165,13 @@
     <t>箱规(高)(cm)</t>
   </si>
   <si>
-    <t>毛重</t>
-  </si>
-  <si>
-    <t>净重</t>
-  </si>
-  <si>
-    <t>单箱重量</t>
+    <t>毛重(g)</t>
+  </si>
+  <si>
+    <t>净重(g)</t>
+  </si>
+  <si>
+    <t>单箱重量(kg)</t>
   </si>
   <si>
     <t>单箱数量</t>
@@ -1238,7 +1238,7 @@
     <col min="23" max="23" width="11" customWidth="1"/>
     <col min="24" max="24" width="9.375"/>
     <col min="26" max="26" width="11.875" style="3" customWidth="1"/>
-    <col min="27" max="27" width="12.5" style="3" customWidth="1"/>
+    <col min="27" max="27" width="12.75" style="3" customWidth="1"/>
     <col min="28" max="28" width="12.125" style="3" customWidth="1"/>
     <col min="29" max="34" width="9" style="3"/>
     <col min="35" max="35" width="9" style="4"/>
@@ -1365,7 +1365,7 @@
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L1048576 AF$1:AF$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L1048576 AF2:AF1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
@@ -1384,7 +1384,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576 AG$1:AH$1048576 Z2:AA1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576 Z2:AA1048576 AG2:AH1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -855,7 +855,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -893,9 +893,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1217,8 +1214,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:AK1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -1358,31 +1355,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="35:37">
-      <c r="AI2" s="13"/>
-      <c r="AJ2" s="13"/>
-      <c r="AK2" s="13"/>
-    </row>
   </sheetData>
-  <dataValidations count="8">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L1048576 AF2:AF1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576 AB2:AC1048576">
+  <dataValidations count="5">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q1 Q2:Q1048576 AB2:AC1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AI2:AI1048576">
       <formula1>0</formula1>
-      <formula2>99999999999999900000</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X1048576">
-      <formula1>25569</formula1>
-      <formula2>72686</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y1048576">
-      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
+      <formula2>999999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576 Z2:AA1048576 AG2:AH1048576">
       <formula1>0</formula1>
@@ -1392,9 +1373,9 @@
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576">
       <formula1>0</formula1>
-      <formula2>999999999999</formula2>
+      <formula2>9999999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -1357,11 +1357,7 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q1 Q2:Q1048576 AB2:AC1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AI2:AI1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576 AB2:AC1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -1377,6 +1373,10 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -1357,7 +1357,11 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576 AB2:AC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q1 Q2:Q1048576 AB2:AC1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AI2:AI1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -1373,10 +1377,6 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="17985" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>spu</t>
   </si>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>保险属性</t>
+  </si>
+  <si>
+    <t>电池重量（g）</t>
   </si>
   <si>
     <r>
@@ -1214,7 +1217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -1226,23 +1229,23 @@
     <col min="13" max="13" width="9.125" customWidth="1"/>
     <col min="14" max="14" width="10.25" customWidth="1"/>
     <col min="15" max="15" width="12.75" customWidth="1"/>
-    <col min="16" max="17" width="12.75" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.75" customWidth="1"/>
-    <col min="19" max="19" width="13.375" customWidth="1"/>
-    <col min="20" max="20" width="11.75" customWidth="1"/>
-    <col min="21" max="21" width="9.875" customWidth="1"/>
-    <col min="22" max="22" width="10" customWidth="1"/>
-    <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="9.375"/>
-    <col min="26" max="26" width="11.875" style="3" customWidth="1"/>
-    <col min="27" max="27" width="12.75" style="3" customWidth="1"/>
-    <col min="28" max="28" width="12.125" style="3" customWidth="1"/>
-    <col min="29" max="34" width="9" style="3"/>
-    <col min="35" max="35" width="9" style="4"/>
-    <col min="36" max="37" width="11.125" style="5" customWidth="1"/>
+    <col min="16" max="18" width="12.75" style="2" customWidth="1"/>
+    <col min="19" max="19" width="13.75" customWidth="1"/>
+    <col min="20" max="20" width="13.375" customWidth="1"/>
+    <col min="21" max="21" width="11.75" customWidth="1"/>
+    <col min="22" max="22" width="9.875" customWidth="1"/>
+    <col min="23" max="23" width="10" customWidth="1"/>
+    <col min="24" max="24" width="11" customWidth="1"/>
+    <col min="25" max="25" width="9.375"/>
+    <col min="27" max="27" width="11.875" style="3" customWidth="1"/>
+    <col min="28" max="28" width="12.75" style="3" customWidth="1"/>
+    <col min="29" max="29" width="12.125" style="3" customWidth="1"/>
+    <col min="30" max="35" width="9" style="3"/>
+    <col min="36" max="36" width="9" style="4"/>
+    <col min="37" max="38" width="11.125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:37">
+    <row r="1" s="1" customFormat="1" spans="1:38">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1294,7 +1297,7 @@
       <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="6" t="s">
@@ -1306,10 +1309,10 @@
       <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="9" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="6" t="s">
@@ -1318,7 +1321,7 @@
       <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="10" t="s">
@@ -1345,37 +1348,40 @@
       <c r="AH1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="11" t="s">
+      <c r="AI1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="12" t="s">
+      <c r="AJ1" s="11" t="s">
         <v>35</v>
       </c>
       <c r="AK1" s="12" t="s">
         <v>36</v>
+      </c>
+      <c r="AL1" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q1 Q2:Q1048576 AB2:AC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576 R$1:R$1048576 AC2:AD1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AI2:AI1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576 Z2:AA1048576 AG2:AH1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576 AA2:AB1048576 AH2:AI1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ$1:AJ$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="17985" windowHeight="4560"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -1363,7 +1363,7 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576 R$1:R$1048576 AC2:AD1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1 Q2:R1048576 AC2:AD1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -147,22 +147,22 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(长)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(宽)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(高)(cm)</t>
+    <t>产品尺寸(长)(mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)(mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(长)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(宽)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(高)(mm)</t>
   </si>
   <si>
     <t>毛重(g)</t>
@@ -1357,11 +1357,7 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q1 Q2:Q1048576 AB2:AC1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AI2:AI1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576 AB2:AC1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -1377,6 +1373,10 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -150,19 +150,19 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(长)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(宽)(cm)</t>
+    <t>产品尺寸(长)(mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)(mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(长)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(宽)(mm)</t>
   </si>
   <si>
     <t>箱规(高)(cm)</t>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -165,7 +165,7 @@
     <t>箱规(宽)(mm)</t>
   </si>
   <si>
-    <t>箱规(高)(cm)</t>
+    <t>箱规(高)(mm)</t>
   </si>
   <si>
     <t>毛重(g)</t>
@@ -1240,7 +1240,9 @@
     <col min="27" max="27" width="11.875" style="3" customWidth="1"/>
     <col min="28" max="28" width="12.75" style="3" customWidth="1"/>
     <col min="29" max="29" width="12.125" style="3" customWidth="1"/>
-    <col min="30" max="35" width="9" style="3"/>
+    <col min="30" max="31" width="9" style="3"/>
+    <col min="32" max="32" width="12.25" style="3" customWidth="1"/>
+    <col min="33" max="35" width="9" style="3"/>
     <col min="36" max="36" width="9" style="4"/>
     <col min="37" max="38" width="11.125" style="5" customWidth="1"/>
   </cols>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateApproveTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>spu</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>申报要素</t>
+  </si>
+  <si>
+    <t>产品质保期</t>
   </si>
   <si>
     <t>英文材质</t>
@@ -1217,7 +1220,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -1236,18 +1239,19 @@
     <col min="22" max="22" width="9.875" customWidth="1"/>
     <col min="23" max="23" width="10" customWidth="1"/>
     <col min="24" max="24" width="11" customWidth="1"/>
-    <col min="25" max="25" width="9.375"/>
-    <col min="27" max="27" width="11.875" style="3" customWidth="1"/>
-    <col min="28" max="28" width="12.75" style="3" customWidth="1"/>
-    <col min="29" max="29" width="12.125" style="3" customWidth="1"/>
-    <col min="30" max="31" width="9" style="3"/>
-    <col min="32" max="32" width="12.25" style="3" customWidth="1"/>
-    <col min="33" max="35" width="9" style="3"/>
-    <col min="36" max="36" width="9" style="4"/>
-    <col min="37" max="38" width="11.125" style="5" customWidth="1"/>
+    <col min="25" max="25" width="10.5" customWidth="1"/>
+    <col min="26" max="26" width="9.375"/>
+    <col min="28" max="28" width="11.875" style="3" customWidth="1"/>
+    <col min="29" max="29" width="12.75" style="3" customWidth="1"/>
+    <col min="30" max="30" width="12.125" style="3" customWidth="1"/>
+    <col min="31" max="32" width="9" style="3"/>
+    <col min="33" max="33" width="12.25" style="3" customWidth="1"/>
+    <col min="34" max="36" width="9" style="3"/>
+    <col min="37" max="37" width="9" style="4"/>
+    <col min="38" max="39" width="11.125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:38">
+    <row r="1" s="1" customFormat="1" spans="1:39">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1326,7 +1330,7 @@
       <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AA1" s="6" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="10" t="s">
@@ -1353,35 +1357,38 @@
       <c r="AI1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="11" t="s">
+      <c r="AJ1" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="12" t="s">
+      <c r="AK1" s="11" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="12" t="s">
         <v>37</v>
+      </c>
+      <c r="AM1" s="12" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1 Q2:R1048576 AC2:AD1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1 Q2:R1048576 AD2:AE1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576 AA2:AB1048576 AH2:AI1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 AI2:AJ1048576 AB2:AC1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ$1:AJ$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK$1:AK$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
